--- a/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,313 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 한 가지에 집중을 못 하겠어요. 창고에서 삐 소리나 지게차 경보음, 아니면 누가 팔레트 옮기는 소리 같은 게 나면 하던 일에서 정신이 팔려요. 그러고 다시 보면 재고 번호를 잘못 입력했다는 걸 알게 되고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 집중력 문제를 겪으신 지 얼마나 되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 달 정도 됐어요. 남편이 바깥일을 그만두고 저희 일상이 바뀌었을 때쯤부터 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 한 달 동안 지속적으로 기분이 가라앉거나 슬프거나 절망적이셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 계속 기분이 가라앉아 있다고는 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 한 달 동안 자주 초조하거나 불안하거나 날이 서 있는 느낌이 드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 불안을 많이 느꼈다고까지는 말 못 하겠어요. 날이 서 있는 느낌도 딱히 못 느꼈고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 어렸을 때 학교 다닐 때도 이런 비슷한 집중력 문제를 겪으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 어릴 때 학교에서 집중하는 데 문제가 있었던 기억은 딱히 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 평소에 즐기시던 일들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 평소 하던 일들에 흥미를 잃었다고는 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 한 달 동안 잠들거나 계속 자는 데 어려움이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 잠들거나 계속 자는 데 특별한 어려움은 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 최근에 평소와 달리 예민해지거나 화를 잘 내게 된 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 어떤 날은 지나치게 들뜬 느낌이 들어요, 마치 저녁 전까지 집이랑 직장 일을 다 해결할 수 있을 것 같은. 근데 남편이 제 계획에 뭔가 의문을 제기하면, 별거 아닌 일로 확 화를 내게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이렇게 평소와 달리 들뜨고 활기 넘치는 시기를 겪으신 게 평생 처음이신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 이번이 처음인지 아닌지 확실히 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 살면서 2주 이상 지속적으로 우울하거나 가라앉거나 절망적이었던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 딱히 그런 시기가 바로 떠오르지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 평소보다 잠을 훨씬 적게 자도 여전히 힘이 넘친다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 잠을 얼마나 자고 있는지 딱히 신경 써서 살펴보지 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 생각이 질주하거나 한 아이디어에서 다른 아이디어로 빠르게 넘어가는 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 정확히 무슨 뜻인지 잘 모르겠어요. 생각이 여기저기 튄다고는 딱히 못 느꼈는데, 그것도 딱히 신경 써서 살펴보지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 본인이나 다른 사람들이, 평소보다 말이 훨씬 많아지거나 빨라진 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 남편이랑 동료들이 제가 가끔 진짜 빨리 말한다고 하더라고요—레시피, 안전 아이디어, 미술 수업 같은 거요—끼어들 틈도 없이요. 생각이 사라지기 전에 다 말해야 할 것 같은 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 이런 기분과 에너지의 변화가 업무 수행이나 일상적인 책임을 감당하는 데 큰 문제를 일으켰나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 조금은요. 직장에서 재고 관련 실수를 좀 해서 상사랑 다시 확인해야 했어요. 그리고 집에서는 남편이랑 말다툼이 많아져서 남편 은퇴 생활에 적응하기보다는 그냥 서로 눈치만 보고 지내는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>진단명: 제1형 양극성장애 (D008)
 인구통계: 성별 여성 / 나이 57 / 직업상태 laborer or freight stock or material mover / 최종학력 대학 재학
@@ -575,371 +873,39 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S039
-배경 서술: 미선의 한 달간 이어진 증상은 남편이 외부 직장에서 은퇴하고 대부분의 시간을 집에서 보내기 시작하면서, 긴 창고 근무 후 그녀가 의지해 온 질서 정연한 가정 리듬이 흐트러지면서 시작됐다. 처음에 그녀는 이 변화를 모든 것을 재정비할 기회로 받아들여, 직장에서 추가 안전 개선 계획을 맡고, 추가 미술 워크숍에 등록하고, 새로운 루틴과 레시피, 자격증 목표에 대해 유난히 강한 열정으로 이야기했다. 늘어난 활동량과 산만함이 재고 실수, 공예 시장에서의 충동구매, 그리고 그녀가 다른 사람들이 따라가지 못할 정도로 계속 확장해 나가는 계획들을 둘러싼 집안에서의 긴장된 말다툼으로 이어지면서 이 변화는 기능을 저해하기 시작했다. 그녀는 감당할 만했던 가족의 전환기가 왜 직장과 결혼 생활의 문제로까지 번졌는지 이해하는 데 도움이 필요하다며 스스로 진료 예약을 잡았고, 그렇게 1차 진료 병원을 통해 정신건강의학과의 주목을 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 한 가지에 집중을 못 하겠어요. 창고에서 삐 소리나 지게차 경보음, 아니면 누가 팔레트 옮기는 소리 같은 게 나면 하던 일에서 정신이 팔려요. 그러고 다시 보면 재고 번호를 잘못 입력했다는 걸 알게 되고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 집중력 문제를 겪으신 지 얼마나 되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 달 정도 됐어요. 남편이 바깥일을 그만두고 저희 일상이 바뀌었을 때쯤부터 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 한 달 동안 지속적으로 기분이 가라앉거나 슬프거나 절망적이셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 계속 기분이 가라앉아 있다고는 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 한 달 동안 자주 초조하거나 불안하거나 날이 서 있는 느낌이 드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 불안을 많이 느꼈다고까지는 말 못 하겠어요. 날이 서 있는 느낌도 딱히 못 느꼈고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 어렸을 때 학교 다닐 때도 이런 비슷한 집중력 문제를 겪으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 어릴 때 학교에서 집중하는 데 문제가 있었던 기억은 딱히 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 평소에 즐기시던 일들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 평소 하던 일들에 흥미를 잃었다고는 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 한 달 동안 잠들거나 계속 자는 데 어려움이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 잠들거나 계속 자는 데 특별한 어려움은 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 최근에 평소와 달리 예민해지거나 화를 잘 내게 된 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 어떤 날은 지나치게 들뜬 느낌이 들어요, 마치 저녁 전까지 집이랑 직장 일을 다 해결할 수 있을 것 같은. 근데 남편이 제 계획에 뭔가 의문을 제기하면, 별거 아닌 일로 확 화를 내게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이렇게 평소와 달리 들뜨고 활기 넘치는 시기를 겪으신 게 평생 처음이신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 이번이 처음인지 아닌지 확실히 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 살면서 2주 이상 지속적으로 우울하거나 가라앉거나 절망적이었던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 딱히 그런 시기가 바로 떠오르지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 평소보다 잠을 훨씬 적게 자도 여전히 힘이 넘친다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 잠을 얼마나 자고 있는지 딱히 신경 써서 살펴보지 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 생각이 질주하거나 한 아이디어에서 다른 아이디어로 빠르게 넘어가는 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 정확히 무슨 뜻인지 잘 모르겠어요. 생각이 여기저기 튄다고는 딱히 못 느꼈는데, 그것도 딱히 신경 써서 살펴보지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 본인이나 다른 사람들이, 평소보다 말이 훨씬 많아지거나 빨라진 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 남편이랑 동료들이 제가 가끔 진짜 빨리 말한다고 하더라고요—레시피, 안전 아이디어, 미술 수업 같은 거요—끼어들 틈도 없이요. 생각이 사라지기 전에 다 말해야 할 것 같은 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 이런 기분과 에너지의 변화가 업무 수행이나 일상적인 책임을 감당하는 데 큰 문제를 일으켰나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 조금은요. 직장에서 재고 관련 실수를 좀 해서 상사랑 다시 확인해야 했어요. 그리고 집에서는 남편이랑 말다툼이 많아져서 남편 은퇴 생활에 적응하기보다는 그냥 서로 눈치만 보고 지내는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+배경 서술: 미선의 한 달간 이어진 증상은 남편이 외부 직장에서 은퇴하고 대부분의 시간을 집에서 보내기 시작하면서, 긴 창고 근무 후 그녀가 의지해 온 질서 정연한 가정 리듬이 흐트러지면서 시작됐다. 처음에 그녀는 이 변화를 모든 것을 재정비할 기회로 받아들여, 직장에서 추가 안전 개선 계획을 맡고, 추가 미술 워크숍에 등록하고, 새로운 루틴과 레시피, 자격증 목표에 대해 유난히 강한 열정으로 이야기했다. 늘어난 활동량과 산만함이 재고 실수, 공예 시장에서의 충동구매, 그리고 그녀가 다른 사람들이 따라가지 못할 정도로 계속 확장해 나가는 계획들을 둘러싼 집안에서의 긴장된 말다툼으로 이어지면서 이 변화는 기능을 저해하기 시작했다. 그녀는 감당할 만했던 가족의 전환기가 왜 직장과 결혼 생활의 문제로까지 번졌는지 이해하는 데 도움이 필요하다며 스스로 진료 예약을 잡았고, 그렇게 1차 진료 병원을 통해 정신건강의학과의 주목을 받게 되었다.
+표집된 증상 목록:
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+  - S041 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
+        </is>
+      </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F30.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
-  누락: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: None (None, ICD: F30.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
@@ -859,6 +859,11 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -901,11 +906,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S005_P002__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0306</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
